--- a/ig/DM_FINESS_New/ValueSet-vs-tre-r405-modalite-activite-smsse-regulee-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-tre-r405-modalite-activite-smsse-regulee-all.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T18:02:28.249+00:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
